--- a/data/tournament_bangalore.xlsx
+++ b/data/tournament_bangalore.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -499,6 +499,19 @@
         <is>
           <t>team_id</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Abhinav</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -764,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -819,6 +832,36 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Abhinav</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
